--- a/IDT_01.xlsx
+++ b/IDT_01.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="213">
   <si>
     <t>SALES DATA</t>
   </si>
@@ -470,6 +470,195 @@
   </si>
   <si>
     <t>fesibility</t>
+  </si>
+  <si>
+    <t>ORDER DATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHIP DATE </t>
+  </si>
+  <si>
+    <t>CATEGORY</t>
+  </si>
+  <si>
+    <t>SUB-CATEGORY</t>
+  </si>
+  <si>
+    <t>QUANTITY</t>
+  </si>
+  <si>
+    <t>PROFIT</t>
+  </si>
+  <si>
+    <t>SHIPPING COST</t>
+  </si>
+  <si>
+    <t>ORDER PRIORITY</t>
+  </si>
+  <si>
+    <t>31-07-2012</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 17-10-2017</t>
+  </si>
+  <si>
+    <t>28-01-2013</t>
+  </si>
+  <si>
+    <t>14-04-2012</t>
+  </si>
+  <si>
+    <t>14/10/2014</t>
+  </si>
+  <si>
+    <t>20-01-2012</t>
+  </si>
+  <si>
+    <t>SEGMENT</t>
+  </si>
+  <si>
+    <t>CITY</t>
+  </si>
+  <si>
+    <t>STATE</t>
+  </si>
+  <si>
+    <t>PRODUCT ID</t>
+  </si>
+  <si>
+    <t>05-02-2013</t>
+  </si>
+  <si>
+    <t>28-06-2013</t>
+  </si>
+  <si>
+    <t>18-10-2013</t>
+  </si>
+  <si>
+    <t>30-01-2013</t>
+  </si>
+  <si>
+    <t>18-04-2012</t>
+  </si>
+  <si>
+    <t>21-10-2014</t>
+  </si>
+  <si>
+    <t>31-01-2010</t>
+  </si>
+  <si>
+    <t>Rich Hansen</t>
+  </si>
+  <si>
+    <t>Justin Ritter</t>
+  </si>
+  <si>
+    <t>Craig Reiter</t>
+  </si>
+  <si>
+    <t>07-11-2013</t>
+  </si>
+  <si>
+    <t>Katherine</t>
+  </si>
+  <si>
+    <t>Rick hansen</t>
+  </si>
+  <si>
+    <t>Jim Mitchum</t>
+  </si>
+  <si>
+    <t>Toby Swindell</t>
+  </si>
+  <si>
+    <t>Mick Brown</t>
+  </si>
+  <si>
+    <t>Jane Waco</t>
+  </si>
+  <si>
+    <t>Joseph Holt</t>
+  </si>
+  <si>
+    <t>Consumer</t>
+  </si>
+  <si>
+    <t>Corporate</t>
+  </si>
+  <si>
+    <t>Home Office</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>Wollongong</t>
+  </si>
+  <si>
+    <t>Brisbane</t>
+  </si>
+  <si>
+    <t>Berlin</t>
+  </si>
+  <si>
+    <t>Dakar</t>
+  </si>
+  <si>
+    <t>New South</t>
+  </si>
+  <si>
+    <t>Wellington</t>
+  </si>
+  <si>
+    <t>Waikato</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>Queensland</t>
+  </si>
+  <si>
+    <t>Sydney</t>
+  </si>
+  <si>
+    <t>Porirua</t>
+  </si>
+  <si>
+    <t>Hamilton</t>
+  </si>
+  <si>
+    <t>Sacramento</t>
+  </si>
+  <si>
+    <t>Concord</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Sengal</t>
+  </si>
+  <si>
+    <t>Newzeland</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Furniture</t>
+  </si>
+  <si>
+    <t>Employee Details</t>
   </si>
 </sst>
 </file>
@@ -508,7 +697,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -518,10 +707,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -854,6 +1044,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1080,11 +1271,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="203872128"/>
-        <c:axId val="203873664"/>
+        <c:axId val="146270080"/>
+        <c:axId val="146271616"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="203872128"/>
+        <c:axId val="146270080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1093,7 +1284,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="203873664"/>
+        <c:crossAx val="146271616"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1101,7 +1292,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="203873664"/>
+        <c:axId val="146271616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1112,13 +1303,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="203872128"/>
+        <c:crossAx val="146270080"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -1163,6 +1355,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1283,11 +1476,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="203927936"/>
-        <c:axId val="203929856"/>
+        <c:axId val="146035072"/>
+        <c:axId val="146036992"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="203927936"/>
+        <c:axId val="146035072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1309,12 +1502,13 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="203929856"/>
+        <c:crossAx val="146036992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1322,7 +1516,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="203929856"/>
+        <c:axId val="146036992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1330,19 +1524,21 @@
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="203927936"/>
+        <c:crossAx val="146035072"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -1387,6 +1583,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1523,11 +1720,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="204133120"/>
-        <c:axId val="204135040"/>
+        <c:axId val="146076416"/>
+        <c:axId val="146078336"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="204133120"/>
+        <c:axId val="146076416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1554,12 +1751,13 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="204135040"/>
+        <c:crossAx val="146078336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1567,7 +1765,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="204135040"/>
+        <c:axId val="146078336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1590,13 +1788,14 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="204133120"/>
+        <c:crossAx val="146076416"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2075,24 +2274,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6">
         <f>SUM(C4:C18)</f>
         <v>99421</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="6"/>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -3469,7 +3668,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -3485,33 +3684,35 @@
     <col min="14" max="14" width="24.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -3543,7 +3744,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -3556,7 +3757,7 @@
       <c r="D4">
         <v>26</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>112</v>
       </c>
       <c r="F4" t="s">
@@ -3576,7 +3777,7 @@
         <v>240000</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -3589,7 +3790,7 @@
       <c r="D5">
         <v>27</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>113</v>
       </c>
       <c r="F5" t="s">
@@ -3609,7 +3810,7 @@
         <v>360000</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -3622,7 +3823,7 @@
       <c r="D6">
         <v>28</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>114</v>
       </c>
       <c r="F6" t="s">
@@ -3642,7 +3843,7 @@
         <v>480000</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -3655,7 +3856,7 @@
       <c r="D7">
         <v>29</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>115</v>
       </c>
       <c r="F7" t="s">
@@ -3675,7 +3876,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -3688,7 +3889,7 @@
       <c r="D8">
         <v>26</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>116</v>
       </c>
       <c r="F8" t="s">
@@ -3708,7 +3909,7 @@
         <v>720000</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -3721,7 +3922,7 @@
       <c r="D9">
         <v>25</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>117</v>
       </c>
       <c r="F9" t="s">
@@ -3741,7 +3942,7 @@
         <v>840000</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -3754,7 +3955,7 @@
       <c r="D10">
         <v>25</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>118</v>
       </c>
       <c r="F10" t="s">
@@ -3773,12 +3974,8 @@
         <f t="shared" si="0"/>
         <v>240000</v>
       </c>
-      <c r="N10" t="str">
-        <f>CONCATENATE("Employee Name :",B4)</f>
-        <v>Employee Name :abdul D</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -3791,7 +3988,7 @@
       <c r="D11">
         <v>21</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>119</v>
       </c>
       <c r="F11" t="s">
@@ -3811,7 +4008,7 @@
         <v>360000</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -3824,7 +4021,7 @@
       <c r="D12">
         <v>30</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>120</v>
       </c>
       <c r="F12" t="s">
@@ -3844,7 +4041,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
@@ -3857,7 +4054,7 @@
       <c r="D13">
         <v>40</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>115</v>
       </c>
       <c r="F13" t="s">
@@ -3877,7 +4074,7 @@
         <v>480000</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -3890,7 +4087,7 @@
       <c r="D14">
         <v>35</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>114</v>
       </c>
       <c r="F14" t="s">
@@ -3910,7 +4107,7 @@
         <v>960000</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -3923,7 +4120,7 @@
       <c r="D15">
         <v>29</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>117</v>
       </c>
       <c r="F15" t="s">
@@ -3943,7 +4140,7 @@
         <v>240000</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
@@ -3956,7 +4153,7 @@
       <c r="D16">
         <v>25</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>119</v>
       </c>
       <c r="F16" t="s">
@@ -3989,7 +4186,7 @@
       <c r="D17">
         <v>23</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>118</v>
       </c>
       <c r="F17" t="s">
@@ -4022,7 +4219,7 @@
       <c r="D18">
         <v>22</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>121</v>
       </c>
       <c r="F18" t="s">
@@ -4055,7 +4252,7 @@
       <c r="D19">
         <v>24</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="5" t="s">
         <v>112</v>
       </c>
       <c r="F19" t="s">
@@ -4088,7 +4285,7 @@
       <c r="D20">
         <v>26</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>114</v>
       </c>
       <c r="F20" t="s">
@@ -4121,7 +4318,7 @@
       <c r="D21">
         <v>32</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="5" t="s">
         <v>120</v>
       </c>
       <c r="F21" t="s">
@@ -4154,7 +4351,7 @@
       <c r="D22">
         <v>34</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="5" t="s">
         <v>117</v>
       </c>
       <c r="F22" t="s">
@@ -4187,7 +4384,7 @@
       <c r="D23">
         <v>31</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="5" t="s">
         <v>113</v>
       </c>
       <c r="F23" t="s">
@@ -4219,9 +4416,358 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <sheetPr codeName="Sheet7"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" t="str">
+        <f>UPPER("CUSTOMER NAME")</f>
+        <v>CUSTOMER NAME</v>
+      </c>
+      <c r="D1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" t="s">
+        <v>167</v>
+      </c>
+      <c r="I1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J1" t="s">
+        <v>153</v>
+      </c>
+      <c r="K1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M1" t="s">
+        <v>155</v>
+      </c>
+      <c r="N1" t="s">
+        <v>156</v>
+      </c>
+      <c r="O1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G2" t="s">
+        <v>205</v>
+      </c>
+      <c r="H2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" s="7">
+        <v>41092</v>
+      </c>
+      <c r="C3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G4" t="s">
+        <v>206</v>
+      </c>
+      <c r="H4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" t="s">
+        <v>192</v>
+      </c>
+      <c r="F5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G5" t="s">
+        <v>207</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" s="7">
+        <v>41436</v>
+      </c>
+      <c r="C6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F6" t="s">
+        <v>193</v>
+      </c>
+      <c r="G6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="7">
+        <v>41281</v>
+      </c>
+      <c r="C7" t="s">
+        <v>181</v>
+      </c>
+      <c r="D7" t="s">
+        <v>187</v>
+      </c>
+      <c r="E7" t="s">
+        <v>199</v>
+      </c>
+      <c r="F7" t="s">
+        <v>194</v>
+      </c>
+      <c r="G7" t="s">
+        <v>206</v>
+      </c>
+      <c r="H7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="7">
+        <v>40735</v>
+      </c>
+      <c r="B8" s="7">
+        <v>40797</v>
+      </c>
+      <c r="C8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F8" t="s">
+        <v>195</v>
+      </c>
+      <c r="G8" t="s">
+        <v>209</v>
+      </c>
+      <c r="H8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" t="s">
+        <v>183</v>
+      </c>
+      <c r="D9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" t="s">
+        <v>196</v>
+      </c>
+      <c r="G9" t="s">
+        <v>209</v>
+      </c>
+      <c r="H9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F10" t="s">
+        <v>197</v>
+      </c>
+      <c r="G10" t="s">
+        <v>205</v>
+      </c>
+      <c r="H10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B11" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D11" t="s">
+        <v>186</v>
+      </c>
+      <c r="E11" t="s">
+        <v>203</v>
+      </c>
+      <c r="F11" t="s">
+        <v>204</v>
+      </c>
+      <c r="G11" t="s">
+        <v>205</v>
+      </c>
+      <c r="H11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>